--- a/outputs/resultats/bns/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bns/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
+        <bgColor rgb="00FDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,10 +72,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -450,6 +462,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,9 +523,848 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>T18 Montants des prêts hypothécaires à l’habitation et des marges de crédit hypothécaires à l’habitation assurés et non assurés, par régions géographiques</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Comprend des immeubles d’habitation (quatre unités ou plus) de 3 505 $ (31 octobre 2024 – 3 796 $), dont une tranche de 2 764 $ est assurée (31 octobre 2024 – 3 024 $).</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Comprend des immeubles d’habitation (quatre unités ou plus) de 3 228 $ (31 janvier 2025 – 3 505 $; 31 octobre 2024 – 3 796 $), dont une tranche de 2 548 $ est assurée (31 janvier 2025 – 2 764 $; 31 octobre 2024 – 3 024 $).</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Les montants financiers ont été mis à jour, ce qui peut affecter l'évaluation des risques et la gestion des actifs immobiliers.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>T18 Montants des prêts hypothécaires à l’habitation et des marges de crédit hypothécaires à l’habitation assurés et non assurés, par régions géographiques</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Les prêts hypothécaires à taux variable représentent 31 % (31 octobre 2024 – 30 %) du total du portefeuille de prêts hypothécaires à l’habitation au Canada.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Les prêts hypothécaires à taux variable représentent 33 % (31 janvier 2025 – 31 %; 31 octobre 2024 – 30 %) du total du portefeuille de prêts hypothécaires à l’habitation au Canada.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>La modification du pourcentage des prêts à taux variable indique un changement dans la composition du portefeuille, ce qui est crucial pour l'analyse des risques de taux d'intérêt.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>T21 Expositions au risque de crédit de la Banque par régions</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Les comptes de correction de valeur pour pertes sur créances s’établissaient à 598 $. Les lettres de crédit et de garanties sont incluses dans les expositions financées puisqu’elles ont été émises. Les prêts et équivalents de prêts comprenaient des lettres de crédit et de garanties d’un montant total de 14 740 $ au 31 janvier 2025 (31 octobre 2024 – 14 446 $).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Les comptes de correction de valeur pour pertes sur créances s’établissaient à 581 $. Les lettres de crédit et de garanties sont incluses dans les expositions financées puisqu’elles ont été émises. Les prêts et équivalents de prêts comprenaient des lettres de crédit et de garanties d’un montant total de 14 272 $ au 30 avril 2025 (31 janvier 2025 – 14 740 $; 31 octobre 2024 – 14 446 $).</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>La modification des montants des comptes de correction de valeur et des lettres de crédit peut indiquer un changement dans l'évaluation des risques de crédit, ce qui est crucial pour l'analyse des expositions financières.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>T21 Expositions au risque de crédit de la Banque par régions</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Les transactions de financement sur titres comprennent des titres pris en pension, des obligations relatives aux titres mis en pension et des transactions de prêt ou d’emprunt de titres. Les expositions financées brutes et nettes représentent la totalité des positions nettes positives, compte tenu des garanties. Les garanties au titre des dérivés s’établissaient à 6 598 $ et celles au titre des transactions de financement sur titres, à 146 315 $.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Les transactions de financement sur titres comprennent des titres pris en pension, des obligations relatives aux titres mis en pension et des transactions de prêt ou d’emprunt de titres. Les expositions financées brutes et nettes représentent la totalité des positions nettes positives, compte tenu des garanties. Les garanties au titre des dérivés s’établissaient à 7 002 $ et celles au titre des transactions de financement sur titres, à 147 502 $.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Les changements dans les montants des garanties pour les dérivés et les transactions de financement sur titres peuvent affecter l'évaluation des risques et la gestion des garanties, ce qui est essentiel pour la gestion des risques financiers.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>T24 Interdépendance du risque de marché et de l’état consolidé de la situation financière de la Banque</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3) Comprend les provisions, les autres passifs et les titres empruntés.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>La suppression de cette note pourrait indiquer un changement dans la présentation des passifs, ce qui peut affecter l'analyse des obligations financières de la Banque.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:46:48.947679+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>T28 Ratio de liquidité à court terme moyen de la Banque¹)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>La présentation de cette information n’est pas exigée aux termes de la ligne directrice.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>La suppression de cette note pourrait indiquer un changement dans les exigences de divulgation, ce qui pourrait avoir un impact sur la transparence réglementaire.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>T29 Ratio structurel de liquidité à long terme de la Banque(1)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Éléments entrant dans le calcul du financement stable requis</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>La suppression de cet indicateur modifie la manière dont le financement stable requis est calculé, ce qui peut affecter l'évaluation de la stabilité financière.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:46:51.519431+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>T32 Ratios de fonds propres réglementaires et de capacité totale d’absorption des pertes</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Risque de levier</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>L'ajout de cet indicateur pourrait refléter un changement dans la manière dont la banque évalue ou présente son exposition au risque de levier, ce qui est crucial pour la gestion des risques et la conformité réglementaire.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:46:49.738712+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>T27 Grèvement d’actifs</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Autres actifs grevés qui ne peuvent être donnés en garantie dans le cours normal des activités comprennent les actifs sous-jacents liés aux structures de titrisation et les actifs donnés en garantie relativement aux obligations sécurisées.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:46:43.274644+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>T27 Grèvement d’actifs</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Actifs non grevés qui peuvent être donnés en garantie dans le cours normal des activités comprennent les prêts admissibles à des programmes de banques centrales et les titres disponibles immédiatement pour être donnés en garantie.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:47:01.333058+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>T27 Grèvement d’actifs</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Autres actifs non grevés qui ne peuvent être donnés en garantie dans le cours normal des activités comprennent les prêts non admissibles à des programmes de banques centrales, les actifs physiques et les autres actifs.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>T27 Grèvement d’actifs</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Comprennent les instruments dérivés, les actifs au titre des transactions de financement de titres et les autres actifs financiers.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>T28 Ratio de liquidité à court terme moyen de la Banque¹)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Pour le trimestre clos le 31janvier 2025 (en millions de dollars)</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Cet indicateur semble être un artefact de date ou de période, et non un indicateur métier réel. Il n'affecte pas l'analyse des ratios de liquidité.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:46:57.397830+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>T33 Indicateurs de BISm</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>T33 Indicateurs de BISm</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Tableau supprimé du trimestre courant.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:46:47.668818+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:N15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bns/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bns/2025_t2_vs_2025_t1/comparison.xlsx
@@ -591,9 +591,21 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19T00:08:32.496067+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -703,9 +715,21 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19T00:08:33.686821+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -823,7 +847,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-18T18:46:48.947679+00:00</t>
+          <t>2026-04-19T00:08:27.047697+00:00</t>
         </is>
       </c>
     </row>
@@ -939,7 +963,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-18T18:46:51.519431+00:00</t>
+          <t>2026-04-19T00:08:36.126494+00:00</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1027,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-18T18:46:49.738712+00:00</t>
+          <t>2026-04-19T00:08:28.104931+00:00</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1091,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18T18:46:43.274644+00:00</t>
+          <t>2026-04-19T00:07:59.165786+00:00</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1155,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18T18:47:01.333058+00:00</t>
+          <t>2026-04-19T00:07:59.323560+00:00</t>
         </is>
       </c>
     </row>
@@ -1183,9 +1207,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-19T00:08:31.167511+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1287,21 +1323,9 @@
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:46:57.397830+00:00</t>
-        </is>
-      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1347,21 +1371,9 @@
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:46:47.668818+00:00</t>
-        </is>
-      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N15"/>

--- a/outputs/resultats/bns/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/bns/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -460,11 +460,10 @@
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,7 +514,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Nouvelle divulgation ?</t>
+          <t>Nouvelle idée ?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -529,11 +528,6 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Validé par</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Validé le</t>
         </is>
@@ -598,12 +592,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:08:32.496067+00:00</t>
+          <t>2026-05-15T01:19:05.653787+00:00</t>
         </is>
       </c>
     </row>
@@ -661,7 +650,6 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -715,21 +703,8 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:08:33.686821+00:00</t>
-        </is>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -785,7 +760,6 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -835,21 +809,8 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:08:27.047697+00:00</t>
-        </is>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -901,7 +862,6 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -958,12 +918,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:08:36.126494+00:00</t>
+          <t>2026-05-15T01:19:20.610668+00:00</t>
         </is>
       </c>
     </row>
@@ -1015,21 +970,8 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:08:28.104931+00:00</t>
-        </is>
-      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1086,12 +1028,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:07:59.165786+00:00</t>
+          <t>2026-05-15T01:18:51.064197+00:00</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1087,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:07:59.323560+00:00</t>
+          <t>2026-05-15T01:18:51.419545+00:00</t>
         </is>
       </c>
     </row>
@@ -1207,21 +1139,8 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-19T00:08:31.167511+00:00</t>
-        </is>
-      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1273,7 +1192,6 @@
       <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1325,7 +1243,6 @@
       <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1371,12 +1288,19 @@
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-15T01:19:46.877348+00:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:M15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>